--- a/Mời đám cưới.xlsx
+++ b/Mời đám cưới.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FileLinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{852A9A90-773B-481B-83A9-581F02F15B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0397DB0-A14B-425F-BF4B-7F81A8FE0866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
   </bookViews>
@@ -37,12 +37,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>Nhóm</t>
   </si>
   <si>
     <t>Tên</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>Trang Hà</t>
+  </si>
+  <si>
+    <t>Tuấn Mỹ</t>
+  </si>
+  <si>
+    <t>Quý Hộ</t>
+  </si>
+  <si>
+    <t>Thành  (Ngọc Hường)</t>
+  </si>
+  <si>
+    <t>Phương Bé</t>
+  </si>
+  <si>
+    <t>Liên Dương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yến </t>
+  </si>
+  <si>
+    <t>Dũng Nhân</t>
+  </si>
+  <si>
+    <t>Đức Vững</t>
+  </si>
+  <si>
+    <t>Đông Đô</t>
+  </si>
+  <si>
+    <t>Tuấn Tự</t>
+  </si>
+  <si>
+    <t>Phương 6</t>
+  </si>
+  <si>
+    <t>Oanh Kiều</t>
+  </si>
+  <si>
+    <t>Phương Chung</t>
+  </si>
+  <si>
+    <t>Hưng Hải</t>
+  </si>
+  <si>
+    <t>Tùng Nghiêm</t>
+  </si>
+  <si>
+    <t>Thiên Đạt</t>
+  </si>
+  <si>
+    <t>Huy Bách</t>
+  </si>
+  <si>
+    <t>Hương Bách</t>
+  </si>
+  <si>
+    <t>Mạnh Đậu</t>
+  </si>
+  <si>
+    <t>Dũng Điển</t>
+  </si>
+  <si>
+    <t>Tuấn Nghi</t>
+  </si>
+  <si>
+    <t>Duy Tương</t>
+  </si>
+  <si>
+    <t>Châm Phương</t>
+  </si>
+  <si>
+    <t>Đại Học</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hùng Nhỏ </t>
+  </si>
+  <si>
+    <t>Hùng To</t>
+  </si>
+  <si>
+    <t>Hằng</t>
+  </si>
+  <si>
+    <t>Trung</t>
+  </si>
+  <si>
+    <t>Trường</t>
+  </si>
+  <si>
+    <t>Tường</t>
+  </si>
+  <si>
+    <t>Thành</t>
+  </si>
+  <si>
+    <t>Thanh</t>
+  </si>
+  <si>
+    <t>Ngọc</t>
+  </si>
+  <si>
+    <t>Hoàng</t>
+  </si>
+  <si>
+    <t>Dương</t>
+  </si>
+  <si>
+    <t>Phong</t>
+  </si>
+  <si>
+    <t>Lệ</t>
+  </si>
+  <si>
+    <t>Hiệp</t>
+  </si>
+  <si>
+    <t>A Duy</t>
+  </si>
+  <si>
+    <t>A Quyết</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Định</t>
+  </si>
+  <si>
+    <t>Hùng Hằng</t>
+  </si>
+  <si>
+    <t>Điệp Trường</t>
+  </si>
+  <si>
+    <t>DFT</t>
+  </si>
+  <si>
+    <t>A Đức</t>
+  </si>
+  <si>
+    <t>Hà</t>
+  </si>
+  <si>
+    <t>Nhung</t>
+  </si>
+  <si>
+    <t>Chu Toàn</t>
+  </si>
+  <si>
+    <t>Nguyên</t>
+  </si>
+  <si>
+    <t>INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thành </t>
+  </si>
+  <si>
+    <t>Tú</t>
+  </si>
+  <si>
+    <t>Trâm</t>
+  </si>
+  <si>
+    <t>Lâm</t>
+  </si>
+  <si>
+    <t>DW</t>
   </si>
 </sst>
 </file>
@@ -86,11 +260,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,11 +580,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C834CCF-EE3F-4620-B7BD-FD036FB851CD}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
@@ -423,6 +598,296 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Mời đám cưới.xlsx
+++ b/Mời đám cưới.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FileLinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0397DB0-A14B-425F-BF4B-7F81A8FE0866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F97517-A39F-44B4-B1AF-5CFA229159DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>Nhóm</t>
   </si>
@@ -213,10 +213,61 @@
     <t>Trâm</t>
   </si>
   <si>
-    <t>Lâm</t>
-  </si>
-  <si>
     <t>DW</t>
+  </si>
+  <si>
+    <t>HN</t>
+  </si>
+  <si>
+    <t>Chi</t>
+  </si>
+  <si>
+    <t>Thái</t>
+  </si>
+  <si>
+    <t>Vân</t>
+  </si>
+  <si>
+    <t>Biên</t>
+  </si>
+  <si>
+    <t>Lâm Bi</t>
+  </si>
+  <si>
+    <t>Oh</t>
+  </si>
+  <si>
+    <t>Thủy</t>
+  </si>
+  <si>
+    <t>Tuấn</t>
+  </si>
+  <si>
+    <t>Bình</t>
+  </si>
+  <si>
+    <t>Quang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mạnh </t>
+  </si>
+  <si>
+    <t>Thảo</t>
+  </si>
+  <si>
+    <t>Chiến</t>
+  </si>
+  <si>
+    <t>Tú A</t>
+  </si>
+  <si>
+    <t>Tú E</t>
+  </si>
+  <si>
+    <t>Hường</t>
+  </si>
+  <si>
+    <t>Hoài</t>
   </si>
 </sst>
 </file>
@@ -580,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C834CCF-EE3F-4620-B7BD-FD036FB851CD}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="2" customWidth="1"/>
@@ -784,6 +835,11 @@
         <v>37</v>
       </c>
     </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>38</v>
@@ -824,68 +880,154 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>59</v>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Mời đám cưới.xlsx
+++ b/Mời đám cưới.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FileLinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F97517-A39F-44B4-B1AF-5CFA229159DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477A4325-615B-474B-95B1-C311D93AA0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
   <si>
     <t>Nhóm</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>Hoài</t>
+  </si>
+  <si>
+    <t>Thêm</t>
+  </si>
+  <si>
+    <t>Tài Tính</t>
   </si>
 </sst>
 </file>
@@ -631,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C834CCF-EE3F-4620-B7BD-FD036FB851CD}">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="2" customWidth="1"/>
@@ -754,279 +760,289 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>76</v>
       </c>
     </row>

--- a/Mời đám cưới.xlsx
+++ b/Mời đám cưới.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FileLinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477A4325-615B-474B-95B1-C311D93AA0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515CCF64-167D-4B55-A50A-BC4AB4B680B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3482B894-DF8E-4F21-BE0D-BB59A98A912F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <si>
     <t>Nhóm</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Tài Tính</t>
+  </si>
+  <si>
+    <t>Kiên SX</t>
   </si>
 </sst>
 </file>
@@ -637,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C834CCF-EE3F-4620-B7BD-FD036FB851CD}">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="2" customWidth="1"/>
@@ -1046,6 +1049,11 @@
         <v>76</v>
       </c>
     </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
